--- a/output/depara_h_cnae_ocde.xlsx
+++ b/output/depara_h_cnae_ocde.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M1333"/>
+  <dimension ref="A1:L1333"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -415,11 +415,6 @@
           <t>cnae_sub_classe_descr</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>ocde_class</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10509,11 +10504,6 @@
           <t>Frigorífico  abate de bovinos</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10574,11 +10564,6 @@
           <t>Frigorífico  abate de equinos</t>
         </is>
       </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10639,11 +10624,6 @@
           <t>Frigorífico  abate de ovinos e caprinos</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10704,11 +10684,6 @@
           <t>Frigorífico  abate de bufalinos</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10769,11 +10744,6 @@
           <t>Matadouro  abate de reses sob contrato, exceto abate de suínos</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10834,11 +10804,6 @@
           <t>Abate de aves</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10899,11 +10864,6 @@
           <t>Abate de pequenos animais</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10964,11 +10924,6 @@
           <t>Frigorífico  abate de suínos</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11029,11 +10984,6 @@
           <t>Matadouro  abate de suínos sob contrato</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11094,11 +11044,6 @@
           <t>Fabricação de produtos de carne</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11159,11 +11104,6 @@
           <t>Preparação de subprodutos do abate</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11224,11 +11164,6 @@
           <t>Preservação de peixes, crustáceos e moluscos</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11289,11 +11224,6 @@
           <t>Fabricação de conservas de peixes, crustáceos e moluscos</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11354,11 +11284,6 @@
           <t>Fabricação de conservas de frutas</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11419,11 +11344,6 @@
           <t>Fabricação de conservas de palmito</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11484,11 +11404,6 @@
           <t>Fabricação de conservas de legumes e outros vegetais, exceto palmito</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11549,11 +11464,6 @@
           <t>Fabricação de sucos concentrados de frutas, hortaliças e legumes</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11614,11 +11524,6 @@
           <t>Fabricação de sucos de frutas, hortaliças e legumes, exceto concentrados</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11679,11 +11584,6 @@
           <t>Fabricação de óleos vegetais em bruto, exceto óleo de milho</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11744,11 +11644,6 @@
           <t>Fabricação de óleos vegetais refinados, exceto óleo de milho</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11809,11 +11704,6 @@
           <t>Fabricação de margarina e outras gorduras vegetais e de óleos não comestíveis de animais</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11874,11 +11764,6 @@
           <t>Preparação do leite</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11939,11 +11824,6 @@
           <t>Fabricação de laticínios</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12004,11 +11884,6 @@
           <t>Fabricação de sorvetes e outros gelados comestíveis</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -12069,11 +11944,6 @@
           <t>Beneficiamento de arroz</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12134,11 +12004,6 @@
           <t>Fabricação de produtos do arroz</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -12199,11 +12064,6 @@
           <t>Moagem de trigo e fabricação de derivados</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -12264,11 +12124,6 @@
           <t>Fabricação de farinha de mandioca e derivados</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -12329,11 +12184,6 @@
           <t>Fabricação de farinha de milho e derivados, exceto óleos de milho</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -12394,11 +12244,6 @@
           <t>Fabricação de amidos e féculas de vegetais</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12459,11 +12304,6 @@
           <t>Fabricação de óleo de milho em bruto</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12524,11 +12364,6 @@
           <t>Fabricação de óleo de milho refinado</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12589,11 +12424,6 @@
           <t>Fabricação de alimentos para animais</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12654,11 +12484,6 @@
           <t>Moagem e fabricação de produtos de origem vegetal não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12719,11 +12544,6 @@
           <t>Fabricação de açúcar em bruto</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12784,11 +12604,6 @@
           <t>Fabricação de açúcar de cana refinado</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12849,11 +12664,6 @@
           <t>Fabricação de açúcar de cereais (dextrose) e de beterraba</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12914,11 +12724,6 @@
           <t>Beneficiamento de café</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12979,11 +12784,6 @@
           <t>Torrefação e moagem de café</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -13044,11 +12844,6 @@
           <t>Fabricação de produtos à base de café</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -13109,11 +12904,6 @@
           <t>Fabricação de produtos de panificação industrial</t>
         </is>
       </c>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -13174,11 +12964,6 @@
           <t>Fabricação de produtos de padaria e confeitaria com predominância de produção própria</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -13239,11 +13024,6 @@
           <t>Fabricação de biscoitos e bolachas</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -13304,11 +13084,6 @@
           <t>Fabricação de produtos derivados do cacau e de chocolates</t>
         </is>
       </c>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -13369,11 +13144,6 @@
           <t>Fabricação de frutas cristalizadas, balas e semelhantes</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -13434,11 +13204,6 @@
           <t>Fabricação de massas alimentícias</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -13499,11 +13264,6 @@
           <t>Fabricação de especiarias, molhos, temperos e condimentos</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13564,11 +13324,6 @@
           <t>Fabricação de alimentos e pratos prontos</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13629,11 +13384,6 @@
           <t>Fabricação de vinagres</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13694,11 +13444,6 @@
           <t>Fabricação de pósalimentícios</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13759,11 +13504,6 @@
           <t>Fabricação de fermentos e leveduras</t>
         </is>
       </c>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13824,11 +13564,6 @@
           <t>Fabricação de gelo comum</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13889,11 +13624,6 @@
           <t>Fabricação de produtos para infusão (chá, mate, etc)</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13954,11 +13684,6 @@
           <t>Fabricação de adoçantes naturais e artificiais</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -14019,11 +13744,6 @@
           <t>Fabricação de alimentos dietéticos e complementos alimentares</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -14084,11 +13804,6 @@
           <t>Fabricação de outros produtos alimentícios não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -14149,11 +13864,6 @@
           <t>Fabricação de aguardente de canadeaçúcar</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -14214,11 +13924,6 @@
           <t>Fabricação de outras aguardentes e bebidas destiladas</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -14279,11 +13984,6 @@
           <t>Fabricação de vinho</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -14344,11 +14044,6 @@
           <t>Fabricação de malte, inclusive malte uísque</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -14409,11 +14104,6 @@
           <t>Fabricação de cervejas e chopes</t>
         </is>
       </c>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -14474,11 +14164,6 @@
           <t>Fabricação de águas envasadas</t>
         </is>
       </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -14539,11 +14224,6 @@
           <t>Fabricação de refrigerantes</t>
         </is>
       </c>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -14604,11 +14284,6 @@
           <t>Fabricação de chá mate e outros chás prontos para consumo</t>
         </is>
       </c>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -14669,11 +14344,6 @@
           <t>Fabricação de refrescos, xaropes e pós para refrescos, exceto refrescos de frutas</t>
         </is>
       </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14734,11 +14404,6 @@
           <t>Fabricação de bebidas isotônicas</t>
         </is>
       </c>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14799,11 +14464,6 @@
           <t>Fabricação de outras bebidas não alcoólicas não especificadas anteriormente</t>
         </is>
       </c>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14864,11 +14524,6 @@
           <t>Processamento industrial do fumo</t>
         </is>
       </c>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14929,11 +14584,6 @@
           <t>Fabricação de cigarros</t>
         </is>
       </c>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14994,11 +14644,6 @@
           <t>Fabricação de cigarrilhas e charutos</t>
         </is>
       </c>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -15059,11 +14704,6 @@
           <t>Fabricação de filtros para cigarros</t>
         </is>
       </c>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -15124,11 +14764,6 @@
           <t>Fabricação de outros produtos do fumo, exceto cigarros, cigarrilhas e charutos</t>
         </is>
       </c>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -15189,11 +14824,6 @@
           <t>Preparação e fiação de fibras de algodão</t>
         </is>
       </c>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -15254,11 +14884,6 @@
           <t>Preparação e fiação de fibras têxteis naturais, exceto algodão</t>
         </is>
       </c>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -15319,11 +14944,6 @@
           <t>Fiação de fibras artificiais e sintéticas</t>
         </is>
       </c>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -15384,11 +15004,6 @@
           <t>Fabricação de linhas para costurar e bordar</t>
         </is>
       </c>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -15449,11 +15064,6 @@
           <t>Tecelagem de fios de algodão</t>
         </is>
       </c>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -15514,11 +15124,6 @@
           <t>Tecelagem de fios de fibras têxteis naturais, exceto algodão</t>
         </is>
       </c>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -15579,11 +15184,6 @@
           <t>Tecelagem de fios de fibras artificiais e sintéticas</t>
         </is>
       </c>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -15644,11 +15244,6 @@
           <t>Fabricação de tecidos de malha</t>
         </is>
       </c>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -15709,11 +15304,6 @@
           <t>Estamparia e texturização em fios, tecidos, artefatos têxteis e peças do vestuário</t>
         </is>
       </c>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -15774,11 +15364,6 @@
           <t>Alvejamento, tingimento e torção em fios, tecidos, artefatos têxteis e peças do vestuário</t>
         </is>
       </c>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -15839,11 +15424,6 @@
           <t>Outros serviços de acabamento em fios, tecidos, artefatos têxteis e peças do vestuário</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -15904,11 +15484,6 @@
           <t>Fabricação de artefatos têxteis para uso doméstico</t>
         </is>
       </c>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -15969,11 +15544,6 @@
           <t>Fabricação de artefatos de tapeçaria</t>
         </is>
       </c>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -16034,11 +15604,6 @@
           <t>Fabricação de artefatos de cordoaria</t>
         </is>
       </c>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -16099,11 +15664,6 @@
           <t>Fabricação de tecidos especiais, inclusive artefatos</t>
         </is>
       </c>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -16164,11 +15724,6 @@
           <t>Fabricação de outros produtos têxteis não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -16229,11 +15784,6 @@
           <t>Confecção de roupas íntimas</t>
         </is>
       </c>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -16294,11 +15844,6 @@
           <t>Facção de roupas íntimas</t>
         </is>
       </c>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -16359,11 +15904,6 @@
           <t>Confecção de peças do vestuário, exceto roupas íntimas e as confeccionadas sob medida</t>
         </is>
       </c>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -16424,11 +15964,6 @@
           <t>Confecção, sob medida, de peças do vestuário, exceto roupas íntimas</t>
         </is>
       </c>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -16489,11 +16024,6 @@
           <t>Facção de peças do vestuário, exceto roupas íntimas</t>
         </is>
       </c>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -16554,11 +16084,6 @@
           <t>Confecção de roupas profissionais, exceto sob medida</t>
         </is>
       </c>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -16619,11 +16144,6 @@
           <t>Confecção, sob medida, de roupas profissionais</t>
         </is>
       </c>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -16684,11 +16204,6 @@
           <t>Facção de roupas profissionais</t>
         </is>
       </c>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -16749,11 +16264,6 @@
           <t>Fabricação de acessórios do vestuário, exceto para segurança e proteção</t>
         </is>
       </c>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -16814,11 +16324,6 @@
           <t>Fabricação de meias</t>
         </is>
       </c>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -16879,11 +16384,6 @@
           <t>Fabricação de artigos do vestuário, produzidos em malharias e tricotagens, exceto meias</t>
         </is>
       </c>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -16944,11 +16444,6 @@
           <t>Curtimento e outras preparações de couro</t>
         </is>
       </c>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -17009,11 +16504,6 @@
           <t>Fabricação de artigos para viagem, bolsas e semelhantes de qualquer material</t>
         </is>
       </c>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -17074,11 +16564,6 @@
           <t>Fabricação de artefatos de couro não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -17139,11 +16624,6 @@
           <t>Fabricação de calçados de couro</t>
         </is>
       </c>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -17204,11 +16684,6 @@
           <t>Acabamento de calçados de couro sob contrato</t>
         </is>
       </c>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -17269,11 +16744,6 @@
           <t>Fabricação de tênis de qualquer material</t>
         </is>
       </c>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -17334,11 +16804,6 @@
           <t>Fabricação de calçados de material sintético</t>
         </is>
       </c>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -17400,11 +16865,6 @@
 anteriormente</t>
         </is>
       </c>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -17465,11 +16925,6 @@
           <t>Fabricação de partes para calçados, de qualquer material</t>
         </is>
       </c>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -17530,11 +16985,6 @@
           <t>Serrarias com desdobramento de madeira em bruto</t>
         </is>
       </c>
-      <c r="M277" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -17595,11 +17045,6 @@
           <t>Serrarias sem desdobramento de madeira em bruto  Resseragem</t>
         </is>
       </c>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -17660,11 +17105,6 @@
           <t>Serviço de tratamento de madeira realizado sob contrato</t>
         </is>
       </c>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -17725,11 +17165,6 @@
           <t>Fabricação de madeira laminada e de chapas de madeira compensada, prensada e aglomerada</t>
         </is>
       </c>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -17790,11 +17225,6 @@
           <t>Fabricação de casas de madeira préfabricadas</t>
         </is>
       </c>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -17855,11 +17285,6 @@
           <t>Fabricação de esquadrias de madeira e de peças de madeira para instalações industriais e comerciais</t>
         </is>
       </c>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -17920,11 +17345,6 @@
           <t>Fabricação de outros artigos de carpintaria para construção</t>
         </is>
       </c>
-      <c r="M283" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -17985,11 +17405,6 @@
           <t>Fabricação de artefatos de tanoaria e de embalagens de madeira</t>
         </is>
       </c>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -18051,11 +17466,6 @@
           <t>Fabricação de artefatos diversos de madeira, exceto móveis</t>
         </is>
       </c>
-      <c r="M285" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -18117,11 +17527,6 @@
           <t>Fabricação de artefatos diversos de cortiça, bambu, palha, vime e outros materiais trançados, exceto móveis</t>
         </is>
       </c>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -18182,11 +17587,6 @@
           <t>Fabricação de celulose e outras pastas para a fabricação de papel</t>
         </is>
       </c>
-      <c r="M287" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -18247,11 +17647,6 @@
           <t>Fabricação de papel</t>
         </is>
       </c>
-      <c r="M288" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -18312,11 +17707,6 @@
           <t>Fabricação de cartolina e papelcartão</t>
         </is>
       </c>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -18377,11 +17767,6 @@
           <t>Fabricação de embalagens de papel</t>
         </is>
       </c>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -18442,11 +17827,6 @@
           <t>Fabricação de embalagens de cartolina e papelcartão</t>
         </is>
       </c>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -18507,11 +17887,6 @@
           <t>Fabricação de chapas e de embalagens de papelão ondulado</t>
         </is>
       </c>
-      <c r="M292" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -18572,11 +17947,6 @@
           <t>Fabricação de formulários contínuos</t>
         </is>
       </c>
-      <c r="M293" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -18637,11 +18007,6 @@
           <t>Fabricação de produtos de papel, cartolina, papelcartão e papelão ondulado para uso comercial e de escritório</t>
         </is>
       </c>
-      <c r="M294" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -18702,11 +18067,6 @@
           <t>Fabricação de fraldas descartáveis</t>
         </is>
       </c>
-      <c r="M295" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -18767,11 +18127,6 @@
           <t>Fabricação de absorventes higiênicos</t>
         </is>
       </c>
-      <c r="M296" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -18832,11 +18187,6 @@
           <t>Fabricação de produtos de papel para uso doméstico e higiênicosanitário não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M297" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -18897,11 +18247,6 @@
           <t>Fabricação de produtos de pastas celulósicas, papel, cartolina, papelcartão e papelão ondulado não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M298" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -18962,11 +18307,6 @@
           <t>Impressão de jornais</t>
         </is>
       </c>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -19027,11 +18367,6 @@
           <t>Impressão de livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
-      <c r="M300" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -19092,11 +18427,6 @@
           <t>Impressão de material de segurança</t>
         </is>
       </c>
-      <c r="M301" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -19157,11 +18487,6 @@
           <t>Impressão de material para uso publicitário</t>
         </is>
       </c>
-      <c r="M302" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -19222,11 +18547,6 @@
           <t>Impressão de material para outros usos</t>
         </is>
       </c>
-      <c r="M303" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -19287,11 +18607,6 @@
           <t>Serviços de préimpressão</t>
         </is>
       </c>
-      <c r="M304" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -19352,11 +18667,6 @@
           <t>Serviços de encadernação e plastificação</t>
         </is>
       </c>
-      <c r="M305" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -19417,11 +18727,6 @@
           <t>Serviços de acabamentos gráficos, exceto encadernação e plastificação</t>
         </is>
       </c>
-      <c r="M306" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -19482,11 +18787,6 @@
           <t>Reprodução de som em qualquer suporte</t>
         </is>
       </c>
-      <c r="M307" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -19547,11 +18847,6 @@
           <t>Reprodução de vídeo em qualquer suporte</t>
         </is>
       </c>
-      <c r="M308" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -19612,11 +18907,6 @@
           <t>Reprodução de software em qualquer suporte</t>
         </is>
       </c>
-      <c r="M309" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -19677,11 +18967,6 @@
           <t>Coquerias</t>
         </is>
       </c>
-      <c r="M310" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -19742,11 +19027,6 @@
           <t>Fabricação de produtos do refino de petróleo</t>
         </is>
       </c>
-      <c r="M311" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -19807,11 +19087,6 @@
           <t>Formulação de combustíveis</t>
         </is>
       </c>
-      <c r="M312" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -19872,11 +19147,6 @@
           <t>Rerrefino de óleos lubrificantes</t>
         </is>
       </c>
-      <c r="M313" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -19937,11 +19207,6 @@
           <t>Fabricação de outros produtos derivados do petróleo, exceto produtos do refino</t>
         </is>
       </c>
-      <c r="M314" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -20002,11 +19267,6 @@
           <t>Fabricação de álcool</t>
         </is>
       </c>
-      <c r="M315" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -20067,11 +19327,6 @@
           <t>Fabricação de biocombustíveis, exceto álcool</t>
         </is>
       </c>
-      <c r="M316" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -20132,11 +19387,6 @@
           <t>Fabricação de cloro e álcalis</t>
         </is>
       </c>
-      <c r="M317" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -20197,11 +19447,6 @@
           <t>Fabricação de intermediários para fertilizantes</t>
         </is>
       </c>
-      <c r="M318" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -20262,11 +19507,6 @@
           <t>Fabricação de adubos e fertilizantes organominerais</t>
         </is>
       </c>
-      <c r="M319" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -20327,11 +19567,6 @@
           <t>Fabricação de adubos e fertilizantes, exceto organominerais</t>
         </is>
       </c>
-      <c r="M320" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -20392,11 +19627,6 @@
           <t>Fabricação de gases industriais</t>
         </is>
       </c>
-      <c r="M321" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -20457,11 +19687,6 @@
           <t>Elaboração de combustíveis nucleares</t>
         </is>
       </c>
-      <c r="M322" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -20522,11 +19747,6 @@
           <t>Fabricação de outros produtos químicos inorgânicos não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -20587,11 +19807,6 @@
           <t>Fabricação de produtos petroquímicos básicos</t>
         </is>
       </c>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -20652,11 +19867,6 @@
           <t>Fabricação de intermediários para plastificantes, resinas e fibras</t>
         </is>
       </c>
-      <c r="M325" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -20717,11 +19927,6 @@
           <t>Fabricação de produtos químicos orgânicos não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M326" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -20782,11 +19987,6 @@
           <t>Fabricação de resinas termoplásticas</t>
         </is>
       </c>
-      <c r="M327" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -20847,11 +20047,6 @@
           <t>Fabricação de resinas termofixas</t>
         </is>
       </c>
-      <c r="M328" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -20912,11 +20107,6 @@
           <t>Fabricação de elastômeros</t>
         </is>
       </c>
-      <c r="M329" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -20977,11 +20167,6 @@
           <t>Fabricação de fibras artificiais e sintéticas</t>
         </is>
       </c>
-      <c r="M330" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -21042,11 +20227,6 @@
           <t>Fabricação de defensivos agrícolas</t>
         </is>
       </c>
-      <c r="M331" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -21107,11 +20287,6 @@
           <t>Fabricação de desinfestantes domissanitários</t>
         </is>
       </c>
-      <c r="M332" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -21172,11 +20347,6 @@
           <t>Fabricação de sabões e detergentes sintéticos</t>
         </is>
       </c>
-      <c r="M333" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -21237,11 +20407,6 @@
           <t>Fabricação de produtos de limpeza e polimento</t>
         </is>
       </c>
-      <c r="M334" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -21302,11 +20467,6 @@
           <t>Fabricação de cosméticos, produtos de perfumaria e de higiene pessoal</t>
         </is>
       </c>
-      <c r="M335" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -21367,11 +20527,6 @@
           <t>Fabricação de tintas, vernizes, esmaltes e lacas</t>
         </is>
       </c>
-      <c r="M336" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -21432,11 +20587,6 @@
           <t>Fabricação de tintas de impressão</t>
         </is>
       </c>
-      <c r="M337" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -21497,11 +20647,6 @@
           <t>Fabricação de impermeabilizantes, solventes e produtos afins</t>
         </is>
       </c>
-      <c r="M338" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -21562,11 +20707,6 @@
           <t>Fabricação de adesivos e selantes</t>
         </is>
       </c>
-      <c r="M339" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -21627,11 +20767,6 @@
           <t>Fabricação de pólvoras, explosivos e detonantes</t>
         </is>
       </c>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -21692,11 +20827,6 @@
           <t>Fabricação de artigos pirotécnicos</t>
         </is>
       </c>
-      <c r="M341" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -21757,11 +20887,6 @@
           <t>Fabricação de fósforos de segurança</t>
         </is>
       </c>
-      <c r="M342" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -21822,11 +20947,6 @@
           <t>Fabricação de aditivos de uso industrial</t>
         </is>
       </c>
-      <c r="M343" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -21887,11 +21007,6 @@
           <t>Fabricação de catalisadores</t>
         </is>
       </c>
-      <c r="M344" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -21952,11 +21067,6 @@
           <t>Fabricação de chapas, filmes, papéis e outros materiais e produtos químicos para fotografia</t>
         </is>
       </c>
-      <c r="M345" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -22017,11 +21127,6 @@
           <t>Fabricação de outros produtos químicos não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M346" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -22082,11 +21187,6 @@
           <t>Fabricação de produtos farmoquímicos</t>
         </is>
       </c>
-      <c r="M347" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -22147,11 +21247,6 @@
           <t>Fabricação de medicamentos alopáticos para uso humano</t>
         </is>
       </c>
-      <c r="M348" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -22212,11 +21307,6 @@
           <t>Fabricação de medicamentos homeopáticos para uso humano</t>
         </is>
       </c>
-      <c r="M349" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -22277,11 +21367,6 @@
           <t>Fabricação de medicamentos fitoterápicos para uso humano</t>
         </is>
       </c>
-      <c r="M350" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -22342,11 +21427,6 @@
           <t>Fabricação de medicamentos para uso veterinário</t>
         </is>
       </c>
-      <c r="M351" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -22407,11 +21487,6 @@
           <t>Fabricação de preparações farmacêuticas</t>
         </is>
       </c>
-      <c r="M352" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -22472,11 +21547,6 @@
           <t>Fabricação de pneumáticos e de câmarasdear</t>
         </is>
       </c>
-      <c r="M353" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -22537,11 +21607,6 @@
           <t>Reforma de pneumáticos usados</t>
         </is>
       </c>
-      <c r="M354" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -22603,11 +21668,6 @@
 anteriormente</t>
         </is>
       </c>
-      <c r="M355" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -22668,11 +21728,6 @@
           <t>Fabricação de laminados planos e tubulares de material plástico</t>
         </is>
       </c>
-      <c r="M356" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -22733,11 +21788,6 @@
           <t>Fabricação de embalagens de material plástico</t>
         </is>
       </c>
-      <c r="M357" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -22798,11 +21848,6 @@
           <t>Fabricação de tubos e acessórios de material plástico para uso na construção</t>
         </is>
       </c>
-      <c r="M358" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -22863,11 +21908,6 @@
           <t>Fabricação de artefatos de material plástico para uso pessoal e doméstico</t>
         </is>
       </c>
-      <c r="M359" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -22928,11 +21968,6 @@
           <t>Fabricação de artefatos de material plástico para usos industriais</t>
         </is>
       </c>
-      <c r="M360" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -22993,11 +22028,6 @@
           <t>Fabricação de artefatos de material plástico para uso na construção, exceto tubos e acessórios</t>
         </is>
       </c>
-      <c r="M361" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -23058,11 +22088,6 @@
           <t>Fabricação de artefatos de material plástico para outros usos não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M362" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -23123,11 +22148,6 @@
           <t>Fabricação de vidro plano e de segurança</t>
         </is>
       </c>
-      <c r="M363" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -23188,11 +22208,6 @@
           <t>Fabricação de embalagens de vidro</t>
         </is>
       </c>
-      <c r="M364" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -23253,11 +22268,6 @@
           <t>Fabricação de artigos de vidro</t>
         </is>
       </c>
-      <c r="M365" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -23318,11 +22328,6 @@
           <t>Fabricação de cimento</t>
         </is>
       </c>
-      <c r="M366" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -23383,11 +22388,6 @@
           <t>Fabricação de estruturas prémoldadas de concreto armado, em série e sob encomenda</t>
         </is>
       </c>
-      <c r="M367" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -23448,11 +22448,6 @@
           <t>Fabricação de artefatos de cimento para uso na construção</t>
         </is>
       </c>
-      <c r="M368" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -23513,11 +22508,6 @@
           <t>Fabricação de artefatos de fibrocimento para uso na construção</t>
         </is>
       </c>
-      <c r="M369" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -23578,11 +22568,6 @@
           <t>Fabricação de casas prémoldadas de concreto</t>
         </is>
       </c>
-      <c r="M370" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -23643,11 +22628,6 @@
           <t>Preparação de massa de concreto e argamassa para construção</t>
         </is>
       </c>
-      <c r="M371" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -23708,11 +22688,6 @@
           <t>Fabricação de outros artefatos e produtos de concreto, cimento, fibrocimento, gesso e materiais semelhantes</t>
         </is>
       </c>
-      <c r="M372" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -23773,11 +22748,6 @@
           <t>Fabricação de produtos cerâmicos refratários</t>
         </is>
       </c>
-      <c r="M373" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -23838,11 +22808,6 @@
           <t>Fabricação de azulejos e pisos</t>
         </is>
       </c>
-      <c r="M374" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -23903,11 +22868,6 @@
           <t>Fabricação de artefatos de cerâmica e barro cozido para uso na construção, exceto azulejos e pisos</t>
         </is>
       </c>
-      <c r="M375" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -23968,11 +22928,6 @@
           <t>Fabricação de material sanitário de cerâmica</t>
         </is>
       </c>
-      <c r="M376" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -24033,11 +22988,6 @@
           <t>Fabricação de produtos cerâmicos não refratários não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M377" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -24098,11 +23048,6 @@
           <t>Britamento de pedras, exceto associado à extração</t>
         </is>
       </c>
-      <c r="M378" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -24163,11 +23108,6 @@
           <t>Aparelhamento de pedras para construção, exceto associado à extração</t>
         </is>
       </c>
-      <c r="M379" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -24228,11 +23168,6 @@
           <t>Aparelhamento de placas e execução de trabalhos em mármore, granito, ardósia e outras pedras</t>
         </is>
       </c>
-      <c r="M380" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -24293,11 +23228,6 @@
           <t>Fabricação de cal e gesso</t>
         </is>
       </c>
-      <c r="M381" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -24358,11 +23288,6 @@
           <t>Decoração, lapidação, gravação, vitrificação e outros trabalhos em cerâmica, louça, vidro e cristal</t>
         </is>
       </c>
-      <c r="M382" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -24423,11 +23348,6 @@
           <t>Fabricação de abrasivos</t>
         </is>
       </c>
-      <c r="M383" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -24488,11 +23408,6 @@
           <t>Fabricação de outros produtos de minerais não metálicos não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M384" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -24553,11 +23468,6 @@
           <t>Produção de ferrogusa</t>
         </is>
       </c>
-      <c r="M385" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -24618,11 +23528,6 @@
           <t>Produção de ferroligas</t>
         </is>
       </c>
-      <c r="M386" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -24683,11 +23588,6 @@
           <t>Produção de semiacabados de aço</t>
         </is>
       </c>
-      <c r="M387" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -24748,11 +23648,6 @@
           <t>Produção de laminados planos de aço ao carbono, revestidos ou não</t>
         </is>
       </c>
-      <c r="M388" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -24813,11 +23708,6 @@
           <t>Produção de laminados planos de aços especiais</t>
         </is>
       </c>
-      <c r="M389" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -24878,11 +23768,6 @@
           <t>Produção de tubos de aço sem costura</t>
         </is>
       </c>
-      <c r="M390" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -24943,11 +23828,6 @@
           <t>Produção de laminados longos de aço, exceto tubos</t>
         </is>
       </c>
-      <c r="M391" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -25008,11 +23888,6 @@
           <t>Produção de arames de aço</t>
         </is>
       </c>
-      <c r="M392" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -25073,11 +23948,6 @@
           <t>Produção de relaminados, trefilados e perfilados de aço, exceto arames</t>
         </is>
       </c>
-      <c r="M393" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -25138,11 +24008,6 @@
           <t>Produção de tubos de aço com costura</t>
         </is>
       </c>
-      <c r="M394" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -25203,11 +24068,6 @@
           <t>Produção de outros tubos de ferro e aço</t>
         </is>
       </c>
-      <c r="M395" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -25268,11 +24128,6 @@
           <t>Produção de alumínio e suas ligas em formas primárias</t>
         </is>
       </c>
-      <c r="M396" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -25333,11 +24188,6 @@
           <t>Produção de laminados de alumínio</t>
         </is>
       </c>
-      <c r="M397" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -25398,11 +24248,6 @@
           <t>Metalurgia dos metais preciosos</t>
         </is>
       </c>
-      <c r="M398" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -25463,11 +24308,6 @@
           <t>Metalurgia do cobre</t>
         </is>
       </c>
-      <c r="M399" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -25528,11 +24368,6 @@
           <t>Produção de zinco em formas primárias</t>
         </is>
       </c>
-      <c r="M400" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -25593,11 +24428,6 @@
           <t>Produção de laminados de zinco</t>
         </is>
       </c>
-      <c r="M401" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -25658,11 +24488,6 @@
           <t>Fabricação de ânodos para galvanoplastia</t>
         </is>
       </c>
-      <c r="M402" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -25723,11 +24548,6 @@
           <t>Metalurgia de outros metais não ferrosos e suas ligas não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M403" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -25788,11 +24608,6 @@
           <t>Fundição de ferro e aço</t>
         </is>
       </c>
-      <c r="M404" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -25853,11 +24668,6 @@
           <t>Fundição de metais não ferrosos e suas ligas</t>
         </is>
       </c>
-      <c r="M405" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -25920,11 +24730,6 @@
           <t>Fabricação de estruturas metálicas</t>
         </is>
       </c>
-      <c r="M406" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -25987,11 +24792,6 @@
           <t>Fabricação de esquadrias de metal</t>
         </is>
       </c>
-      <c r="M407" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -26054,11 +24854,6 @@
           <t>Fabricação de obras de caldeiraria pesada</t>
         </is>
       </c>
-      <c r="M408" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -26120,11 +24915,6 @@
           <t>Fabricação de tanques, reservatórios metálicos e caldeiras para aquecimento central</t>
         </is>
       </c>
-      <c r="M409" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -26186,11 +24976,6 @@
           <t>Fabricação de caldeiras geradoras de vapor, exceto para aquecimento central e para veículos</t>
         </is>
       </c>
-      <c r="M410" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -26252,11 +25037,6 @@
           <t>Produção de forjados de aço</t>
         </is>
       </c>
-      <c r="M411" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -26318,11 +25098,6 @@
           <t>Produção de forjados de metais não ferrosos e suas ligas</t>
         </is>
       </c>
-      <c r="M412" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -26384,11 +25159,6 @@
           <t>Produção de artefatos estampados de metal</t>
         </is>
       </c>
-      <c r="M413" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -26450,11 +25220,6 @@
           <t>Metalurgia do pó</t>
         </is>
       </c>
-      <c r="M414" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -26516,11 +25281,6 @@
           <t>Serviços de usinagem, torneiria e solda</t>
         </is>
       </c>
-      <c r="M415" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -26582,11 +25342,6 @@
           <t>Serviços de tratamento e revestimento em metais</t>
         </is>
       </c>
-      <c r="M416" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -26648,11 +25403,6 @@
           <t>Fabricação de artigos de cutelaria</t>
         </is>
       </c>
-      <c r="M417" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -26714,11 +25464,6 @@
           <t>Fabricação de artigos de serralheria, exceto esquadrias</t>
         </is>
       </c>
-      <c r="M418" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -26780,11 +25525,6 @@
           <t>Fabricação de ferramentas</t>
         </is>
       </c>
-      <c r="M419" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -26846,11 +25586,6 @@
           <t>Fabricação de equipamento bélico pesado, exceto veículos militares de combate</t>
         </is>
       </c>
-      <c r="M420" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -26912,11 +25647,6 @@
           <t>Fabricação de armas de fogo, outras armas e munições</t>
         </is>
       </c>
-      <c r="M421" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -26978,11 +25708,6 @@
           <t>Fabricação de embalagens metálicas</t>
         </is>
       </c>
-      <c r="M422" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -27044,11 +25769,6 @@
           <t>Fabricação de produtos de trefilados de metal padronizados</t>
         </is>
       </c>
-      <c r="M423" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -27110,11 +25830,6 @@
           <t>Fabricação de produtos de trefilados de metal, exceto padronizados</t>
         </is>
       </c>
-      <c r="M424" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -27176,11 +25891,6 @@
           <t>Fabricação de artigos de metal para uso doméstico e pessoal</t>
         </is>
       </c>
-      <c r="M425" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -27242,11 +25952,6 @@
           <t>Serviços de confecção de armações metálicas para a construção</t>
         </is>
       </c>
-      <c r="M426" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -27308,11 +26013,6 @@
           <t>Serviço de corte e dobra de metais</t>
         </is>
       </c>
-      <c r="M427" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -27374,11 +26074,6 @@
           <t>Fabricação de outros produtos de metal não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M428" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -27439,11 +26134,6 @@
           <t>Fabricação de componentes eletrônicos</t>
         </is>
       </c>
-      <c r="M429" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -27504,11 +26194,6 @@
           <t>Fabricação de equipamentos de informática</t>
         </is>
       </c>
-      <c r="M430" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -27569,11 +26254,6 @@
           <t>Fabricação de periféricos para equipamentos de informática</t>
         </is>
       </c>
-      <c r="M431" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -27634,11 +26314,6 @@
           <t>Fabricação de equipamentos transmissores de comunicação, peças e acessórios</t>
         </is>
       </c>
-      <c r="M432" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -27699,11 +26374,6 @@
           <t>Fabricação de aparelhos telefônicos e de outros equipamentos de comunicação, peças e acessórios</t>
         </is>
       </c>
-      <c r="M433" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -27764,11 +26434,6 @@
           <t>Fabricação de aparelhos de recepção, reprodução, gravação e amplificação de áudio e vídeo</t>
         </is>
       </c>
-      <c r="M434" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -27830,11 +26495,6 @@
           <t>Fabricação de aparelhos e equipamentos de medida, teste e controle</t>
         </is>
       </c>
-      <c r="M435" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -27895,11 +26555,6 @@
           <t>Fabricação de cronômetros e relógios</t>
         </is>
       </c>
-      <c r="M436" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -27960,11 +26615,6 @@
           <t>Fabricação de aparelhos eletromédicos e eletroterapêuticos e equipamentos de irradiação</t>
         </is>
       </c>
-      <c r="M437" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -28025,11 +26675,6 @@
           <t>Fabricação de equipamentos e instrumentos ópticos, peças e acessórios</t>
         </is>
       </c>
-      <c r="M438" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -28090,11 +26735,6 @@
           <t>Fabricação de aparelhos fotográficos e cinematográficos, peças e acessórios</t>
         </is>
       </c>
-      <c r="M439" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -28155,11 +26795,6 @@
           <t>Fabricação de mídias virgens, magnéticas e ópticas</t>
         </is>
       </c>
-      <c r="M440" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -28220,11 +26855,6 @@
           <t>Fabricação de geradores de corrente contínua e alternada, peças e acessórios</t>
         </is>
       </c>
-      <c r="M441" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -28285,11 +26915,6 @@
           <t>Fabricação de transformadores, indutores, conversores, sincronizadores e semelhantes, peças e acessórios</t>
         </is>
       </c>
-      <c r="M442" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -28350,11 +26975,6 @@
           <t>Fabricação de motores elétricos, peças e acessórios</t>
         </is>
       </c>
-      <c r="M443" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -28415,11 +27035,6 @@
           <t>Fabricação de pilhas, baterias e acumuladores elétricos, exceto para veículos automotores</t>
         </is>
       </c>
-      <c r="M444" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -28480,11 +27095,6 @@
           <t>Fabricação de baterias e acumuladores para veículos automotores</t>
         </is>
       </c>
-      <c r="M445" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -28545,11 +27155,6 @@
           <t>Recondicionamento de baterias e acumuladores para veículos automotores</t>
         </is>
       </c>
-      <c r="M446" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -28610,11 +27215,6 @@
           <t>Fabricação de aparelhos e equipamentos para distribuição e controle de energia elétrica</t>
         </is>
       </c>
-      <c r="M447" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -28675,11 +27275,6 @@
           <t>Fabricação de material elétrico para instalações em circuito de consumo</t>
         </is>
       </c>
-      <c r="M448" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -28740,11 +27335,6 @@
           <t>Fabricação de fios, cabos e condutores elétricos isolados</t>
         </is>
       </c>
-      <c r="M449" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -28805,11 +27395,6 @@
           <t>Fabricação de lâmpadas</t>
         </is>
       </c>
-      <c r="M450" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -28870,11 +27455,6 @@
           <t>Fabricação de luminárias e outros equipamentos de iluminação</t>
         </is>
       </c>
-      <c r="M451" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -28935,11 +27515,6 @@
           <t>Fabricação de fogões, refrigeradores e máquinas de lavar e secar para uso doméstico, peças e acessórios</t>
         </is>
       </c>
-      <c r="M452" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -29000,11 +27575,6 @@
           <t>Fabricação de aparelhos elétricos de uso pessoal, peças e acessórios</t>
         </is>
       </c>
-      <c r="M453" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -29065,11 +27635,6 @@
           <t>Fabricação de outros aparelhos eletrodomésticos não especificados anteriormente, peças e acessórios</t>
         </is>
       </c>
-      <c r="M454" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -29130,11 +27695,6 @@
           <t>Fabricação de eletrodos, contatos e outros artigos de carvão e grafita para uso elétrico, eletroímãs e isoladores</t>
         </is>
       </c>
-      <c r="M455" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -29195,11 +27755,6 @@
           <t>Fabricação de equipamentos para sinalização e alarme</t>
         </is>
       </c>
-      <c r="M456" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -29260,11 +27815,6 @@
           <t>Fabricação de outros equipamentos e aparelhos elétricos não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M457" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -29325,11 +27875,6 @@
           <t>Fabricação de motores e turbinas, peças e acessórios, exceto para aviões e veículos rodoviários</t>
         </is>
       </c>
-      <c r="M458" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -29390,11 +27935,6 @@
           <t>Fabricação de equipamentos hidráulicos e pneumáticos, peças e acessórios, exceto válvulas</t>
         </is>
       </c>
-      <c r="M459" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -29455,11 +27995,6 @@
           <t>Fabricação de válvulas, registros e dispositivos semelhantes, peças e acessórios</t>
         </is>
       </c>
-      <c r="M460" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -29520,11 +28055,6 @@
           <t>Fabricação de compressores para uso industrial, peças e acessórios</t>
         </is>
       </c>
-      <c r="M461" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -29585,11 +28115,6 @@
           <t>Fabricação de compressores para uso não industrial, peças e acessórios</t>
         </is>
       </c>
-      <c r="M462" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -29650,11 +28175,6 @@
           <t>Fabricação de rolamentos para fins industriais</t>
         </is>
       </c>
-      <c r="M463" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -29715,11 +28235,6 @@
           <t>Fabricação de equipamentos de transmissão para fins industriais, exceto rolamentos</t>
         </is>
       </c>
-      <c r="M464" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -29780,11 +28295,6 @@
           <t>Fabricação de fornos industriais, aparelhos e equipamentos não elétricos para instalações térmicas, peças e acessórios</t>
         </is>
       </c>
-      <c r="M465" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -29845,11 +28355,6 @@
           <t>Fabricação de estufas e fornos elétricos para fins industriais, peças e acessórios</t>
         </is>
       </c>
-      <c r="M466" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -29910,11 +28415,6 @@
           <t>Fabricação de máquinas, equipamentos e aparelhos para transporte e elevação de pessoas, peças e acessórios</t>
         </is>
       </c>
-      <c r="M467" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -29975,11 +28475,6 @@
           <t>Fabricação de máquinas, equipamentos e aparelhos para transporte e elevação de cargas, peças e acessórios</t>
         </is>
       </c>
-      <c r="M468" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -30040,11 +28535,6 @@
           <t>Fabricação de máquinas e aparelhos de refrigeração e ventilação para uso industrial e comercial, peças e acessórios</t>
         </is>
       </c>
-      <c r="M469" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -30105,11 +28595,6 @@
           <t>Fabricação de aparelhos e equipamentos de ar condicionado para uso industrial</t>
         </is>
       </c>
-      <c r="M470" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -30170,11 +28655,6 @@
           <t>Fabricação de aparelhos e equipamentos de ar condicionado para uso não industrial</t>
         </is>
       </c>
-      <c r="M471" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -30235,11 +28715,6 @@
           <t>Fabricação de máquinas e equipamentos para saneamento básico e ambiental, peças e acessórios</t>
         </is>
       </c>
-      <c r="M472" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -30300,11 +28775,6 @@
           <t>Fabricação de máquinas de escrever, calcular e outros equipamentos não eletrônicos para escritório, peças e acessórios</t>
         </is>
       </c>
-      <c r="M473" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -30365,11 +28835,6 @@
           <t>Fabricação de outras máquinas e equipamentos de uso geral não especificados anteriormente, peças e acessórios</t>
         </is>
       </c>
-      <c r="M474" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -30430,11 +28895,6 @@
           <t>Fabricação de tratores agrícolas, peças e acessórios</t>
         </is>
       </c>
-      <c r="M475" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -30495,11 +28955,6 @@
           <t>Fabricação de equipamentos para irrigação agrícola, peças e acessórios</t>
         </is>
       </c>
-      <c r="M476" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -30560,11 +29015,6 @@
           <t>Fabricação de máquinas e equipamentos para a agricultura e pecuária, peças e acessórios, exceto para irrigação</t>
         </is>
       </c>
-      <c r="M477" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -30625,11 +29075,6 @@
           <t>Fabricação de máquinasferramenta, peças e acessórios</t>
         </is>
       </c>
-      <c r="M478" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -30690,11 +29135,6 @@
           <t>Fabricação de máquinas e equipamentos para a prospecção e extração de petróleo, peças e acessórios</t>
         </is>
       </c>
-      <c r="M479" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -30755,11 +29195,6 @@
           <t>Fabricação de outras máquinas e equipamentos para uso na extração mineral, peças e acessórios, exceto na extração de petróleo</t>
         </is>
       </c>
-      <c r="M480" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -30820,11 +29255,6 @@
           <t>Fabricação de tratores, peças e acessórios, exceto agrícolas</t>
         </is>
       </c>
-      <c r="M481" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -30885,11 +29315,6 @@
           <t>Fabricação de máquinas e equipamentos para terraplenagem, pavimentação e construção, peças e acessórios, exceto tratores</t>
         </is>
       </c>
-      <c r="M482" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -30950,11 +29375,6 @@
           <t>Fabricação de máquinas para a indústria metalúrgica, peças e acessórios, exceto máquinasferramenta</t>
         </is>
       </c>
-      <c r="M483" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -31015,11 +29435,6 @@
           <t>Fabricação de máquinas e equipamentos para as indústrias de alimentos, bebidas e fumo, peças e acessórios</t>
         </is>
       </c>
-      <c r="M484" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -31080,11 +29495,6 @@
           <t>Fabricação de máquinas e equipamentos para a indústria têxtil, peças e acessórios</t>
         </is>
       </c>
-      <c r="M485" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -31145,11 +29555,6 @@
           <t>Fabricação de máquinas e equipamentos para as indústrias do vestuário, do couro e de calçados, peças e acessórios</t>
         </is>
       </c>
-      <c r="M486" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -31210,11 +29615,6 @@
           <t>Fabricação de máquinas e equipamentos para as indústrias de celulose, papel e papelão e artefatos, peças e acessórios</t>
         </is>
       </c>
-      <c r="M487" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -31275,11 +29675,6 @@
           <t>Fabricação de máquinas e equipamentos para a indústria do plástico, peças e acessórios</t>
         </is>
       </c>
-      <c r="M488" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -31340,11 +29735,6 @@
           <t>Fabricação de máquinas e equipamentos para uso industrial específico não especificados anteriormente, peças e acessórios</t>
         </is>
       </c>
-      <c r="M489" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -31405,11 +29795,6 @@
           <t>Fabricação de automóveis, camionetas e utilitários</t>
         </is>
       </c>
-      <c r="M490" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -31470,11 +29855,6 @@
           <t>Fabricação de chassis com motor para automóveis, camionetas e utilitários</t>
         </is>
       </c>
-      <c r="M491" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -31535,11 +29915,6 @@
           <t>Fabricação de motores para automóveis, camionetas e utilitários</t>
         </is>
       </c>
-      <c r="M492" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -31600,11 +29975,6 @@
           <t>Fabricação de caminhões e ônibus</t>
         </is>
       </c>
-      <c r="M493" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -31665,11 +30035,6 @@
           <t>Fabricação de motores para caminhões e ônibus</t>
         </is>
       </c>
-      <c r="M494" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -31730,11 +30095,6 @@
           <t>Fabricação de cabines, carrocerias e reboques para caminhões</t>
         </is>
       </c>
-      <c r="M495" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -31795,11 +30155,6 @@
           <t>Fabricação de carrocerias para ônibus</t>
         </is>
       </c>
-      <c r="M496" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -31860,11 +30215,6 @@
           <t>Fabricação de cabines, carrocerias e reboques para outros veículos automotores, exceto caminhões e ônibus</t>
         </is>
       </c>
-      <c r="M497" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -31925,11 +30275,6 @@
           <t>Fabricação de peças e acessórios para o sistema motor de veículos automotores</t>
         </is>
       </c>
-      <c r="M498" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -31990,11 +30335,6 @@
           <t>Fabricação de peças e acessórios para os sistemas de marcha e transmissão de veículos automotores</t>
         </is>
       </c>
-      <c r="M499" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -32055,11 +30395,6 @@
           <t>Fabricação de peças e acessórios para o sistema de freios de veículos automotores</t>
         </is>
       </c>
-      <c r="M500" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -32120,11 +30455,6 @@
           <t>Fabricação de peças e acessórios para o sistema de direção e suspensão de veículos automotores</t>
         </is>
       </c>
-      <c r="M501" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -32185,11 +30515,6 @@
           <t>Fabricação de material elétrico e eletrônico para veículos automotores, exceto baterias</t>
         </is>
       </c>
-      <c r="M502" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -32250,11 +30575,6 @@
           <t>Fabricação de bancos e estofados para veículos automotores</t>
         </is>
       </c>
-      <c r="M503" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -32315,11 +30635,6 @@
           <t>Fabricação de outras peças e acessórios para veículos automotores não especificadas anteriormente</t>
         </is>
       </c>
-      <c r="M504" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -32380,11 +30695,6 @@
           <t>Recondicionamento e recuperação de motores para veículos automotores</t>
         </is>
       </c>
-      <c r="M505" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -32445,11 +30755,6 @@
           <t>Construção de embarcações de grande porte</t>
         </is>
       </c>
-      <c r="M506" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -32510,11 +30815,6 @@
           <t>Construção de embarcações para uso comercial e para usos especiais, exceto de grande porte</t>
         </is>
       </c>
-      <c r="M507" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -32575,11 +30875,6 @@
           <t>Construção de embarcações para esporte e lazer</t>
         </is>
       </c>
-      <c r="M508" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -32640,11 +30935,6 @@
           <t>Fabricação de locomotivas, vagões e outros materiais rodantes</t>
         </is>
       </c>
-      <c r="M509" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -32705,11 +30995,6 @@
           <t>Fabricação de peças e acessórios para veículos ferroviários</t>
         </is>
       </c>
-      <c r="M510" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -32770,11 +31055,6 @@
           <t>Fabricação de aeronaves</t>
         </is>
       </c>
-      <c r="M511" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -32835,11 +31115,6 @@
           <t>Fabricação de turbinas, motores e outros componentes e peças para aeronaves</t>
         </is>
       </c>
-      <c r="M512" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -32900,11 +31175,6 @@
           <t>Fabricação de veículos militares de combate</t>
         </is>
       </c>
-      <c r="M513" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -32965,11 +31235,6 @@
           <t>Fabricação de motocicletas</t>
         </is>
       </c>
-      <c r="M514" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -33030,11 +31295,6 @@
           <t>Fabricação de peças e acessórios para motocicletas</t>
         </is>
       </c>
-      <c r="M515" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -33095,11 +31355,6 @@
           <t>Fabricação de bicicletas e triciclos não motorizados, peças e acessórios</t>
         </is>
       </c>
-      <c r="M516" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -33160,11 +31415,6 @@
           <t>Fabricação de equipamentos de transporte não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M517" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -33225,11 +31475,6 @@
           <t>Fabricação de móveis com predominância de madeira</t>
         </is>
       </c>
-      <c r="M518" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -33290,11 +31535,6 @@
           <t>Fabricação de móveis com predominância de metal</t>
         </is>
       </c>
-      <c r="M519" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -33355,11 +31595,6 @@
           <t>Fabricação de móveis de outros materiais, exceto madeira e metal</t>
         </is>
       </c>
-      <c r="M520" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -33420,11 +31655,6 @@
           <t>Fabricação de colchões</t>
         </is>
       </c>
-      <c r="M521" t="inlineStr">
-        <is>
-          <t>Média Baixa</t>
-        </is>
-      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -33485,11 +31715,6 @@
           <t>Lapidação de gemas</t>
         </is>
       </c>
-      <c r="M522" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -33550,11 +31775,6 @@
           <t>Fabricação de artefatos de joalheria e ourivesaria</t>
         </is>
       </c>
-      <c r="M523" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -33615,11 +31835,6 @@
           <t>Cunhagem de moedas e medalhas</t>
         </is>
       </c>
-      <c r="M524" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -33680,11 +31895,6 @@
           <t>Fabricação de bijuterias e artefatos semelhantes</t>
         </is>
       </c>
-      <c r="M525" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -33745,11 +31955,6 @@
           <t>Fabricação de instrumentos musicais, peças e acessórios</t>
         </is>
       </c>
-      <c r="M526" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -33810,11 +32015,6 @@
           <t>Fabricação de artefatos para pesca e esporte</t>
         </is>
       </c>
-      <c r="M527" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -33875,11 +32075,6 @@
           <t>Fabricação de jogos eletrônicos</t>
         </is>
       </c>
-      <c r="M528" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -33940,11 +32135,6 @@
           <t>Fabricação de mesas de bilhar, de sinuca e acessórios não associada à locação</t>
         </is>
       </c>
-      <c r="M529" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -34005,11 +32195,6 @@
           <t>Fabricação de mesas de bilhar, de sinuca e acessórios associada à locação</t>
         </is>
       </c>
-      <c r="M530" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -34070,11 +32255,6 @@
           <t>Fabricação de outros brinquedos e jogos recreativos não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M531" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -34135,11 +32315,6 @@
           <t>Fabricação de instrumentos não eletrônicos e utensílios para uso médico, cirúrgico, odontológico e de laboratório</t>
         </is>
       </c>
-      <c r="M532" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -34200,11 +32375,6 @@
           <t>Fabricação de mobiliário para uso médico, cirúrgico, odontológico e de laboratório</t>
         </is>
       </c>
-      <c r="M533" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -34265,11 +32435,6 @@
           <t>Fabricação de aparelhos e utensílios para correção de defeitos físicos e aparelhos ortopédicos em geral sob encomenda</t>
         </is>
       </c>
-      <c r="M534" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -34330,11 +32495,6 @@
           <t>Fabricação de aparelhos e utensílios para correção de defeitos físicos e aparelhos ortopédicos em geral, exceto sob encomenda</t>
         </is>
       </c>
-      <c r="M535" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -34395,11 +32555,6 @@
           <t>Fabricação de materiais para medicina e odontologia</t>
         </is>
       </c>
-      <c r="M536" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -34460,11 +32615,6 @@
           <t>Serviços de prótese dentária</t>
         </is>
       </c>
-      <c r="M537" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -34525,11 +32675,6 @@
           <t>Fabricação de artigos ópticos</t>
         </is>
       </c>
-      <c r="M538" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -34590,11 +32735,6 @@
           <t>Serviço de laboratório óptico</t>
         </is>
       </c>
-      <c r="M539" t="inlineStr">
-        <is>
-          <t>Média Alta</t>
-        </is>
-      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -34655,11 +32795,6 @@
           <t>Fabricação de escovas, pincéis e vassouras</t>
         </is>
       </c>
-      <c r="M540" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -34720,11 +32855,6 @@
           <t>Fabricação de roupas de proteção e segurança e resistentes a fogo</t>
         </is>
       </c>
-      <c r="M541" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -34785,11 +32915,6 @@
           <t>Fabricação de equipamentos e acessórios para segurança pessoal e profissional</t>
         </is>
       </c>
-      <c r="M542" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -34850,11 +32975,6 @@
           <t>Fabricação de guardachuvas e similares</t>
         </is>
       </c>
-      <c r="M543" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -34915,11 +33035,6 @@
           <t>Fabricação de canetas, lápis e outros artigos para escritório</t>
         </is>
       </c>
-      <c r="M544" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -34980,11 +33095,6 @@
           <t>Fabricação de letras, letreiros e placas de qualquer material, exceto luminosos</t>
         </is>
       </c>
-      <c r="M545" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -35045,11 +33155,6 @@
           <t>Fabricação de painéis e letreiros luminosos</t>
         </is>
       </c>
-      <c r="M546" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -35110,11 +33215,6 @@
           <t>Fabricação de aviamentos para costura</t>
         </is>
       </c>
-      <c r="M547" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -35175,11 +33275,6 @@
           <t>Fabricação de velas, inclusive decorativas</t>
         </is>
       </c>
-      <c r="M548" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -35240,11 +33335,6 @@
           <t>Fabricação de produtos diversos não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M549" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -35305,11 +33395,6 @@
           <t>Manutenção e reparação de tanques, reservatórios metálicos e caldeiras, exceto para veículos</t>
         </is>
       </c>
-      <c r="M550" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -35370,11 +33455,6 @@
           <t>Manutenção e reparação de aparelhos e instrumentos de medida, teste e controle</t>
         </is>
       </c>
-      <c r="M551" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -35435,11 +33515,6 @@
           <t>Manutenção e reparação de aparelhos eletromédicos e eletroterapêuticos e equipamentos de irradiação</t>
         </is>
       </c>
-      <c r="M552" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -35500,11 +33575,6 @@
           <t>Manutenção e reparação de equipamentos e instrumentos ópticos</t>
         </is>
       </c>
-      <c r="M553" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -35565,11 +33635,6 @@
           <t>Manutenção e reparação de geradores, transformadores e motores elétricos</t>
         </is>
       </c>
-      <c r="M554" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -35630,11 +33695,6 @@
           <t>Manutenção e reparação de baterias e acumuladores elétricos, exceto para veículos</t>
         </is>
       </c>
-      <c r="M555" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -35695,11 +33755,6 @@
           <t>Manutenção e reparação de máquinas, aparelhos e materiais elétricos não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M556" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -35760,11 +33815,6 @@
           <t>Manutenção e reparação de máquinas motrizes não elétricas</t>
         </is>
       </c>
-      <c r="M557" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -35825,11 +33875,6 @@
           <t>Manutenção e reparação de equipamentos hidráulicos e pneumáticos, exceto válvulas</t>
         </is>
       </c>
-      <c r="M558" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -35890,11 +33935,6 @@
           <t>Manutenção e reparação de válvulas industriais</t>
         </is>
       </c>
-      <c r="M559" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -35955,11 +33995,6 @@
           <t>Manutenção e reparação de compressores</t>
         </is>
       </c>
-      <c r="M560" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -36020,11 +34055,6 @@
           <t>Manutenção e reparação de equipamentos de transmissão para fins industriais</t>
         </is>
       </c>
-      <c r="M561" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -36085,11 +34115,6 @@
           <t>Manutenção e reparação de máquinas, aparelhos e equipamentos para instalações térmicas</t>
         </is>
       </c>
-      <c r="M562" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -36150,11 +34175,6 @@
           <t>Manutenção e reparação de máquinas e aparelhos de refrigeração e ventilação para uso industrial e comercial</t>
         </is>
       </c>
-      <c r="M563" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -36215,11 +34235,6 @@
           <t>Manutenção e reparação de máquinas, equipamentos e aparelhos para transporte e elevação de cargas</t>
         </is>
       </c>
-      <c r="M564" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -36280,11 +34295,6 @@
           <t>Manutenção e reparação de máquinas de escrever, calcular e de outros equipamentos não eletrônicos para escritório</t>
         </is>
       </c>
-      <c r="M565" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -36345,11 +34355,6 @@
           <t>Manutenção e reparação de máquinas e equipamentos para uso geral não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M566" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -36410,11 +34415,6 @@
           <t>Manutenção e reparação de máquinas e equipamentos para agricultura e pecuária</t>
         </is>
       </c>
-      <c r="M567" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -36475,11 +34475,6 @@
           <t>Manutenção e reparação de tratores agrícolas</t>
         </is>
       </c>
-      <c r="M568" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -36540,11 +34535,6 @@
           <t>Manutenção e reparação de máquinasferramenta</t>
         </is>
       </c>
-      <c r="M569" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -36605,11 +34595,6 @@
           <t>Manutenção e reparação de máquinas e equipamentos para a prospecção e extração de petróleo</t>
         </is>
       </c>
-      <c r="M570" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -36670,11 +34655,6 @@
           <t>Manutenção e reparação de máquinas e equipamentos para uso na extração mineral, exceto na extração de petróleo</t>
         </is>
       </c>
-      <c r="M571" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -36735,11 +34715,6 @@
           <t>Manutenção e reparação de tratores, exceto agrícolas</t>
         </is>
       </c>
-      <c r="M572" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -36800,11 +34775,6 @@
           <t>Manutenção e reparação de máquinas e equipamentos de terraplenagem, pavimentação e construção, exceto tratores</t>
         </is>
       </c>
-      <c r="M573" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -36865,11 +34835,6 @@
           <t>Manutenção e reparação de máquinas para a indústria metalúrgica, exceto máquinasferramenta</t>
         </is>
       </c>
-      <c r="M574" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -36930,11 +34895,6 @@
           <t>Manutenção e reparação de máquinas e equipamentos para as indústrias de alimentos, bebidas e fumo</t>
         </is>
       </c>
-      <c r="M575" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -36995,11 +34955,6 @@
           <t>Manutenção e reparação de máquinas e equipamentos para a indústria têxtil, do vestuário, do couro e calçados</t>
         </is>
       </c>
-      <c r="M576" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -37060,11 +35015,6 @@
           <t>Manutenção e reparação de máquinas e aparelhos para a indústria de celulose, papel e papelão e artefatos</t>
         </is>
       </c>
-      <c r="M577" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -37125,11 +35075,6 @@
           <t>Manutenção e reparação de máquinas e aparelhos para a indústria do plástico</t>
         </is>
       </c>
-      <c r="M578" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -37190,11 +35135,6 @@
           <t>Manutenção e reparação de outras máquinas e equipamentos para usos industriais não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M579" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -37255,11 +35195,6 @@
           <t>Manutenção e reparação de veículos ferroviários</t>
         </is>
       </c>
-      <c r="M580" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -37320,11 +35255,6 @@
           <t>Manutenção e reparação de aeronaves, exceto a manutenção na pista</t>
         </is>
       </c>
-      <c r="M581" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -37385,11 +35315,6 @@
           <t>Manutenção de aeronaves na pista</t>
         </is>
       </c>
-      <c r="M582" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -37450,11 +35375,6 @@
           <t>Manutenção e reparação de embarcações e estruturas flutuantes</t>
         </is>
       </c>
-      <c r="M583" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -37515,11 +35435,6 @@
           <t>Manutenção e reparação de embarcações para esporte e lazer</t>
         </is>
       </c>
-      <c r="M584" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -37580,11 +35495,6 @@
           <t>Manutenção e reparação de equipamentos e produtos não especificados anteriormente</t>
         </is>
       </c>
-      <c r="M585" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -37645,11 +35555,6 @@
           <t>Instalação de máquinas e equipamentos industriais</t>
         </is>
       </c>
-      <c r="M586" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -37710,11 +35615,6 @@
           <t>Serviços de montagem de móveis de qualquer material</t>
         </is>
       </c>
-      <c r="M587" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -37773,11 +35673,6 @@
       <c r="L588" t="inlineStr">
         <is>
           <t>Instalação de outros equipamentos não especificados anteriormente</t>
-        </is>
-      </c>
-      <c r="M588" t="inlineStr">
-        <is>
-          <t>Média</t>
         </is>
       </c>
     </row>
